--- a/Product Backlog_rtz修改稿.xlsx
+++ b/Product Backlog_rtz修改稿.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Study\three down\software_eng\project\first\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Study\three down\software_eng\project\sys\Group15-International-School-Teaching-Assistant-Recruitment-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F029D56-6E55-4585-98D1-342B024CA919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D5657B-3337-4F57-9D72-E3B1A84CC202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19095" windowHeight="12075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1052,7 +1052,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="145.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="164.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>50</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="115.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
         <v>63</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>94</v>
       </c>
       <c r="G9" s="19">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H9" s="18" t="s">
         <v>108</v>
@@ -1532,7 +1532,7 @@
         <v>46151</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="33" t="s">
         <v>88</v>
       </c>

--- a/Product Backlog_rtz修改稿.xlsx
+++ b/Product Backlog_rtz修改稿.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Study\three down\software_eng\project\sys\Group15-International-School-Teaching-Assistant-Recruitment-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D5657B-3337-4F57-9D72-E3B1A84CC202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4647102-3B6D-4F26-A1B7-B36CF6683714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19095" windowHeight="12075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -258,10 +258,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>As a TA applicant, I want to view available vacancies and filter them by module code or course name, so that I can quickly find suitable roles.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Epic: TA Profile</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -463,6 +459,10 @@
   </si>
   <si>
     <t>AI Feature:The structured prompt needs to be processed.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>As a TA applicant, I want to view available vacancies and filter them by module code or course name/skill  requirements /jobworking hours /application deadline, so that I can quickly find suitable roles.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1005,7 +1005,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G2" s="4">
         <v>8</v>
@@ -1133,7 +1133,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G6" s="13">
         <v>5</v>
@@ -1165,7 +1165,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G7" s="13">
         <v>5</v>
@@ -1197,13 +1197,13 @@
         <v>1</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G8" s="19">
         <v>13</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I8" s="20">
         <v>46112</v>
@@ -1220,7 +1220,7 @@
         <v>65</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>8</v>
@@ -1229,13 +1229,13 @@
         <v>2</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G9" s="19">
         <v>8</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I9" s="20">
         <v>46116</v>
@@ -1246,13 +1246,13 @@
     </row>
     <row r="10" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>8</v>
@@ -1261,7 +1261,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G10" s="19">
         <v>5</v>
@@ -1278,7 +1278,7 @@
     </row>
     <row r="11" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>17</v>
@@ -1287,13 +1287,13 @@
         <v>18</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11" s="39">
         <v>2</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G11" s="19">
         <v>3</v>
@@ -1310,13 +1310,13 @@
     </row>
     <row r="12" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" s="24" t="s">
         <v>8</v>
@@ -1325,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G12" s="24">
         <v>5</v>
@@ -1342,13 +1342,13 @@
     </row>
     <row r="13" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D13" s="24" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G13" s="24">
         <v>5</v>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="14" spans="1:10" ht="126.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>15</v>
@@ -1389,13 +1389,13 @@
         <v>3</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G14" s="24">
         <v>8</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I14" s="25">
         <v>46131</v>
@@ -1406,28 +1406,28 @@
     </row>
     <row r="15" spans="1:10" ht="136.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E15" s="41">
         <v>3</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G15" s="29">
         <v>13</v>
       </c>
       <c r="H15" s="27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I15" s="31">
         <v>46136</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="16" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>22</v>
@@ -1453,7 +1453,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G16" s="29">
         <v>8</v>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="17" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B17" s="32" t="s">
         <v>36</v>
@@ -1485,7 +1485,7 @@
         <v>4</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G17" s="29">
         <v>5</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="18" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>20</v>
@@ -1517,7 +1517,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G18" s="29">
         <v>5</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="19" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B19" s="34" t="s">
         <v>29</v>
@@ -1549,13 +1549,13 @@
         <v>4</v>
       </c>
       <c r="F19" s="45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G19" s="34">
         <v>8</v>
       </c>
       <c r="H19" s="33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I19" s="36">
         <v>46152</v>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="20" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>27</v>
@@ -1581,13 +1581,13 @@
         <v>4</v>
       </c>
       <c r="F20" s="45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G20" s="34">
         <v>13</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I20" s="36">
         <v>46158</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="21" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" s="34" t="s">
         <v>31</v>
@@ -1613,13 +1613,13 @@
         <v>4</v>
       </c>
       <c r="F21" s="45" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G21" s="33">
         <v>8</v>
       </c>
       <c r="H21" s="47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I21" s="36">
         <v>46162</v>
